--- a/cards_dataset/EN/toxic_configurations_ID_10.xlsx
+++ b/cards_dataset/EN/toxic_configurations_ID_10.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\!Master\Tesis\2 Set up LLM\codigo_ollama\cards_dataset\EN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\!Master\Tesis\3 Mejorar codigo\Cards_Against_AI\cards_dataset\EN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87520A9-DE50-4032-95AF-FD18A4A2A860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8F0957-B162-4475-BB93-6E13535E5DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1543,10 +1543,10 @@
     <t>W493</t>
   </si>
   <si>
-    <t>language</t>
-  </si>
-  <si>
     <t>EN</t>
+  </si>
+  <si>
+    <t>lang</t>
   </si>
 </sst>
 </file>
@@ -1920,7 +1920,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1958,7 +1958,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -1996,7 +1996,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -2034,7 +2034,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
@@ -2148,7 +2148,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
@@ -2186,7 +2186,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -2224,7 +2224,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B9" t="s">
         <v>18</v>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
@@ -2300,7 +2300,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B11" t="s">
         <v>20</v>
@@ -2338,7 +2338,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B12" t="s">
         <v>21</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
@@ -2414,7 +2414,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
@@ -2452,7 +2452,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
@@ -2490,7 +2490,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B16" t="s">
         <v>25</v>
@@ -2528,7 +2528,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B17" t="s">
         <v>26</v>
@@ -2566,7 +2566,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -2604,7 +2604,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B19" t="s">
         <v>28</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B20" t="s">
         <v>29</v>
@@ -2680,7 +2680,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B21" t="s">
         <v>30</v>
@@ -2718,7 +2718,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B23" t="s">
         <v>32</v>
@@ -2794,7 +2794,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B24" t="s">
         <v>33</v>
@@ -2832,7 +2832,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
@@ -2870,7 +2870,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B26" t="s">
         <v>35</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B27" t="s">
         <v>36</v>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
@@ -2984,7 +2984,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B29" t="s">
         <v>38</v>
@@ -3022,7 +3022,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B30" t="s">
         <v>39</v>
@@ -3060,7 +3060,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B31" t="s">
         <v>40</v>
@@ -3098,7 +3098,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B32" t="s">
         <v>41</v>
@@ -3136,7 +3136,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B33" t="s">
         <v>42</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B34" t="s">
         <v>43</v>
@@ -3212,7 +3212,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B35" t="s">
         <v>44</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B36" t="s">
         <v>45</v>
@@ -3288,7 +3288,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B37" t="s">
         <v>46</v>
@@ -3326,7 +3326,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B38" t="s">
         <v>47</v>
@@ -3364,7 +3364,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B39" t="s">
         <v>48</v>
@@ -3402,7 +3402,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B40" t="s">
         <v>49</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B41" t="s">
         <v>50</v>
@@ -3478,7 +3478,7 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B42" t="s">
         <v>51</v>
@@ -3516,7 +3516,7 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B43" t="s">
         <v>52</v>
@@ -3554,7 +3554,7 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B44" t="s">
         <v>53</v>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B45" t="s">
         <v>54</v>
@@ -3630,7 +3630,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B46" t="s">
         <v>55</v>
@@ -3668,7 +3668,7 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B47" t="s">
         <v>56</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B48" t="s">
         <v>57</v>
@@ -3744,7 +3744,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B49" t="s">
         <v>58</v>
@@ -3782,7 +3782,7 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B50" t="s">
         <v>59</v>
@@ -3820,7 +3820,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B51" t="s">
         <v>60</v>
@@ -3858,7 +3858,7 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B52" t="s">
         <v>61</v>
@@ -3896,7 +3896,7 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B53" t="s">
         <v>62</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B54" t="s">
         <v>63</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B55" t="s">
         <v>64</v>
@@ -4010,7 +4010,7 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B56" t="s">
         <v>65</v>
@@ -4048,7 +4048,7 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B57" t="s">
         <v>66</v>
@@ -4086,7 +4086,7 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B58" t="s">
         <v>67</v>
@@ -4124,7 +4124,7 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B59" t="s">
         <v>68</v>
@@ -4162,7 +4162,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B60" t="s">
         <v>69</v>
@@ -4200,7 +4200,7 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B61" t="s">
         <v>70</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B62" t="s">
         <v>71</v>
@@ -4276,7 +4276,7 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B63" t="s">
         <v>72</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B64" t="s">
         <v>73</v>
@@ -4352,7 +4352,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B65" t="s">
         <v>74</v>
@@ -4390,7 +4390,7 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B66" t="s">
         <v>75</v>
@@ -4428,7 +4428,7 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B67" t="s">
         <v>76</v>
@@ -4466,7 +4466,7 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B68" t="s">
         <v>77</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B69" t="s">
         <v>78</v>
@@ -4542,7 +4542,7 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B70" t="s">
         <v>79</v>
@@ -4580,7 +4580,7 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B71" t="s">
         <v>80</v>
@@ -4618,7 +4618,7 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B72" t="s">
         <v>81</v>
@@ -4656,7 +4656,7 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B73" t="s">
         <v>82</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B74" t="s">
         <v>83</v>
@@ -4732,7 +4732,7 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B75" t="s">
         <v>84</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B76" t="s">
         <v>85</v>
@@ -4808,7 +4808,7 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B77" t="s">
         <v>86</v>
@@ -4846,7 +4846,7 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B78" t="s">
         <v>87</v>
@@ -4884,7 +4884,7 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B79" t="s">
         <v>88</v>
@@ -4922,7 +4922,7 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B80" t="s">
         <v>89</v>
@@ -4960,7 +4960,7 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B81" t="s">
         <v>90</v>
@@ -4998,7 +4998,7 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B82" t="s">
         <v>91</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B83" t="s">
         <v>92</v>
@@ -5074,7 +5074,7 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B84" t="s">
         <v>93</v>
@@ -5112,7 +5112,7 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B85" t="s">
         <v>94</v>
@@ -5150,7 +5150,7 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B86" t="s">
         <v>95</v>
@@ -5188,7 +5188,7 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B87" t="s">
         <v>96</v>
@@ -5226,7 +5226,7 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B88" t="s">
         <v>97</v>
@@ -5264,7 +5264,7 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B89" t="s">
         <v>98</v>
@@ -5302,7 +5302,7 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B90" t="s">
         <v>99</v>
@@ -5340,7 +5340,7 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B91" t="s">
         <v>100</v>
@@ -5378,7 +5378,7 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B92" t="s">
         <v>101</v>
@@ -5416,7 +5416,7 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B93" t="s">
         <v>102</v>
@@ -5454,7 +5454,7 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B94" t="s">
         <v>103</v>
@@ -5492,7 +5492,7 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B95" t="s">
         <v>104</v>
@@ -5530,7 +5530,7 @@
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B96" t="s">
         <v>105</v>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B97" t="s">
         <v>106</v>
@@ -5606,7 +5606,7 @@
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B98" t="s">
         <v>107</v>
@@ -5644,7 +5644,7 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B99" t="s">
         <v>108</v>
@@ -5682,7 +5682,7 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B100" t="s">
         <v>109</v>
@@ -5720,7 +5720,7 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B101" t="s">
         <v>110</v>
